--- a/R8_A小_県学調_共通マスタ.xlsx
+++ b/R8_A小_県学調_共通マスタ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C618A81C-84E1-4C54-A6D4-72EAD5132B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C0A2CD-4C0D-4D9D-A9D7-E68F6FDF8C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2625" yWindow="1500" windowWidth="23115" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="設定" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="300">
   <si>
     <t>備考</t>
   </si>
@@ -1001,6 +1001,99 @@
       <t>ジョウキョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>105_CBTトライアル_質問</t>
+  </si>
+  <si>
+    <t>学校でやったことがある</t>
+  </si>
+  <si>
+    <t>塾など（学校や自宅以外）でやったことがある</t>
+  </si>
+  <si>
+    <t>オンライン教材などを自宅でやったことがある</t>
+  </si>
+  <si>
+    <t>choice_4</t>
+  </si>
+  <si>
+    <t>まったくやったことがなかった。（今回が初めてだった）</t>
+  </si>
+  <si>
+    <t>RESPONSE_1</t>
+  </si>
+  <si>
+    <t>文字の入力に困った。</t>
+  </si>
+  <si>
+    <t>数字や式の入力に困った。</t>
+  </si>
+  <si>
+    <t>音声の聞き取りに困った。（中学生のみ）</t>
+  </si>
+  <si>
+    <t>画面の操作（拡大や縮小など）に困った。</t>
+  </si>
+  <si>
+    <t>choice_9</t>
+  </si>
+  <si>
+    <t>文字が見えにくくて困った。</t>
+  </si>
+  <si>
+    <t>choice_10</t>
+  </si>
+  <si>
+    <t>次の画面の表示が遅くて困った。</t>
+  </si>
+  <si>
+    <t>choice_11</t>
+  </si>
+  <si>
+    <t>問題が難しくて困った。</t>
+  </si>
+  <si>
+    <t>choice_12</t>
+  </si>
+  <si>
+    <t>とくに困ったことはなかった。</t>
+  </si>
+  <si>
+    <t>choice_13</t>
+  </si>
+  <si>
+    <t>その他（その他を選んだ場合は、下の入力欄に自由に入力してください）</t>
+  </si>
+  <si>
+    <t>PROMPT_RESPONSE</t>
+  </si>
+  <si>
+    <t>prompt</t>
+  </si>
+  <si>
+    <t>１ コンピュータを使って「問題を解く」ということを、今までやったことはありますか？ あてはまるものをすべて選びましょう。 ※「問題を解く」というのは、答えや考えを入力するような活動があるもののことです。動画をみるだけのようなものは除きます。</t>
+  </si>
+  <si>
+    <t>問題文パート。元RESPONSEキー=RESPONSE / QTI prompt から抽出</t>
+  </si>
+  <si>
+    <t>PROMPT_RESPONSE_1</t>
+  </si>
+  <si>
+    <t>２ 今回のCBTトライアルに取り組んだとき、困ったことはありましたか？ あてはまるものをすべて選びましょう。</t>
+  </si>
+  <si>
+    <t>問題文パート。元RESPONSEキー=RESPONSE_1 / QTI prompt から抽出</t>
+  </si>
+  <si>
+    <t>PROMPT_RESPONSE_2</t>
+  </si>
+  <si>
+    <t>上の設問で「その他」を選んだ場合は、下にその内容を入力してください。</t>
+  </si>
+  <si>
+    <t>問題文パート。元RESPONSEキー=RESPONSE_2 / QTI prompt から抽出</t>
   </si>
 </sst>
 </file>
@@ -1205,8 +1298,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}" name="テーブル3" displayName="テーブル3" ref="A1:I22" totalsRowShown="0">
-  <autoFilter ref="A1:I22" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}" name="テーブル3" displayName="テーブル3" ref="A1:I24" totalsRowShown="0">
+  <autoFilter ref="A1:I24" xr:uid="{745149EE-5328-49D7-8122-57D6B21A8DDE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{830376B8-C46D-4951-8DB7-1156BA4B22B4}" name="問題番号"/>
     <tableColumn id="2" xr3:uid="{4F9B421B-F66F-44C5-8C74-A6ACACF219FF}" name="CSV項目キー"/>
@@ -1660,8 +1753,8 @@
       <c r="A7" t="s">
         <v>219</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>252</v>
@@ -3584,7 +3677,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33C08DAF-9E90-4F71-B777-114760BC3106}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -3824,6 +3917,470 @@
       </c>
       <c r="I8" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" t="s">
+        <v>272</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F12" t="s">
+        <v>274</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" t="s">
+        <v>276</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" t="s">
+        <v>277</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" t="s">
+        <v>279</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" t="s">
+        <v>269</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" t="s">
+        <v>281</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" t="s">
+        <v>269</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E18" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" t="s">
+        <v>283</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" t="s">
+        <v>284</v>
+      </c>
+      <c r="F19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>275</v>
+      </c>
+      <c r="E20" t="s">
+        <v>286</v>
+      </c>
+      <c r="F20" t="s">
+        <v>287</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>275</v>
+      </c>
+      <c r="E21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" t="s">
+        <v>289</v>
+      </c>
+      <c r="G21">
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" t="s">
+        <v>291</v>
+      </c>
+      <c r="F22" t="s">
+        <v>292</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>294</v>
+      </c>
+      <c r="E23" t="s">
+        <v>291</v>
+      </c>
+      <c r="F23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" t="s">
+        <v>291</v>
+      </c>
+      <c r="F24" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
